--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y88"/>
+  <dimension ref="A1:Y90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Every Subp Ã¦ ena,</t>
+          <t>L73: stray/suspicious non-ASCII glyph(s): U+FF10 FULLWIDTH DIGIT ZERO | symbol-only separator/garbage line :: 1 ０</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]153</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]153</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L11: isolated marker/symbol line :: 5.</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L7: isolated marker/symbol line :: t</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]153</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -645,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -656,12 +660,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: 1 ï¼�</t>
+          <t>L74: stray/suspicious non-ASCII glyph(s): U+FF11 FULLWIDTH DIGIT ONE, U+FF10 FULLWIDTH DIGIT ZERO | symbol-only separator/garbage line :: １ ０</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L135: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L135: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -673,7 +677,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L17: symbol-only separator/garbage line :: .50</t>
+          <t>L7: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -713,11 +717,7 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L74: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: ï¼‘ ï¼�</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
@@ -728,7 +728,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: 10</t>
+          <t>L17: symbol-only separator/garbage line :: .50</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -754,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L21: symbol-only separator/garbage line :: .5 0</t>
+          <t>L19: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -830,7 +830,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L22: isolated marker/symbol line :: 50</t>
+          <t>L21: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L24: symbol-only separator/garbage line :: - 0 0</t>
+          <t>L22: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -932,7 +932,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L24: symbol-only separator/garbage line :: - 0 0</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 10</t>
+          <t>L26: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: F,</t>
+          <t>L83: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L87: symbol-only separator/garbage line :: 10 0</t>
+          <t>L85: isolated marker/symbol line :: F,</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L91: symbol-only separator/garbage line :: &gt; 10 0</t>
+          <t>L87: symbol-only separator/garbage line :: 10 0</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L93: symbol-only separator/garbage line :: 25 0</t>
+          <t>L91: symbol-only separator/garbage line :: &gt; 10 0</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: r</t>
+          <t>L93: symbol-only separator/garbage line :: 25 0</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L96: symbol-only separator/garbage line :: )42 0</t>
+          <t>L95: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 10</t>
+          <t>L96: symbol-only separator/garbage line :: )42 0</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: e</t>
+          <t>L98: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 13</t>
+          <t>L100: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L106: symbol-only separator/garbage line :: ,10</t>
+          <t>L105: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L107: symbol-only separator/garbage line :: .10</t>
+          <t>L106: symbol-only separator/garbage line :: ,10</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: r</t>
+          <t>L107: symbol-only separator/garbage line :: .10</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L111: symbol-only separator/garbage line :: .5 0</t>
+          <t>L108: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L113: symbol-only separator/garbage line :: 5 0</t>
+          <t>L111: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: A</t>
+          <t>L113: symbol-only separator/garbage line :: 5 0</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 10</t>
+          <t>L115: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L118: symbol-only separator/garbage line :: .10</t>
+          <t>L117: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L120: symbol-only separator/garbage line :: 0 6</t>
+          <t>L118: symbol-only separator/garbage line :: .10</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L121: symbol-only separator/garbage line :: .5 0</t>
+          <t>L120: symbol-only separator/garbage line :: 0 6</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L123: symbol-only separator/garbage line :: 5 0</t>
+          <t>L121: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L125: symbol-only separator/garbage line :: .2 6</t>
+          <t>L123: symbol-only separator/garbage line :: 5 0</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 04</t>
+          <t>L125: symbol-only separator/garbage line :: .2 6</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L129: symbol-only separator/garbage line :: .50</t>
+          <t>L127: isolated marker/symbol line :: 04</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L131: symbol-only separator/garbage line :: 1 3</t>
+          <t>L129: symbol-only separator/garbage line :: .50</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: L</t>
+          <t>L131: symbol-only separator/garbage line :: 1 3</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L135: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L133: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2015,10 +2015,14 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 04</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="inlineStr"/>
+          <t>L73: stray/suspicious non-ASCII glyph(s): U+FF10 FULLWIDTH DIGIT ZERO | symbol-only separator/garbage line :: 1 ０</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L135: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2046,7 +2050,7 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 0</t>
+          <t>L74: stray/suspicious non-ASCII glyph(s): U+FF11 FULLWIDTH DIGIT ONE, U+FF10 FULLWIDTH DIGIT ZERO | symbol-only separator/garbage line :: １ ０</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -2077,7 +2081,7 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 4</t>
+          <t>L76: isolated marker/symbol line :: 04</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2108,7 +2112,7 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 2</t>
+          <t>L77: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2139,7 +2143,7 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 6</t>
+          <t>L78: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2170,7 +2174,7 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 3</t>
+          <t>L79: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2201,7 +2205,7 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 0</t>
+          <t>L80: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2232,7 +2236,7 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L84: symbol-only separator/garbage line :: 5 0</t>
+          <t>L81: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2263,7 +2267,7 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 0</t>
+          <t>L82: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2294,7 +2298,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: 6</t>
+          <t>L84: symbol-only separator/garbage line :: 5 0</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2325,7 +2329,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 1</t>
+          <t>L86: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2356,7 +2360,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 0</t>
+          <t>L87: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2387,7 +2391,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 2</t>
+          <t>L89: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2418,7 +2422,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 6</t>
+          <t>L90: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2449,7 +2453,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 1</t>
+          <t>L92: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2480,7 +2484,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 0</t>
+          <t>L93: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2511,7 +2515,7 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: 1</t>
+          <t>L95: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -2542,7 +2546,7 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 0</t>
+          <t>L96: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -2573,7 +2577,7 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 4</t>
+          <t>L97: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -2604,7 +2608,7 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L114: isolated marker/symbol line :: L</t>
+          <t>L98: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -2635,7 +2639,7 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: 5</t>
+          <t>L101: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -2666,7 +2670,7 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 0</t>
+          <t>L114: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -2697,7 +2701,7 @@
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 5</t>
+          <t>L115: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -2728,7 +2732,7 @@
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 0</t>
+          <t>L116: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -2759,7 +2763,7 @@
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L119: isolated marker/symbol line :: 5</t>
+          <t>L117: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -2790,7 +2794,7 @@
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: 0</t>
+          <t>L118: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -2821,7 +2825,7 @@
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: 2</t>
+          <t>L119: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -2852,7 +2856,7 @@
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: 6</t>
+          <t>L120: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -2883,7 +2887,7 @@
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: 0</t>
+          <t>L121: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -2914,7 +2918,7 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 4</t>
+          <t>L122: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -2945,7 +2949,7 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L125: isolated marker/symbol line :: 5</t>
+          <t>L123: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -2976,7 +2980,7 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: 0</t>
+          <t>L124: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3007,7 +3011,7 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L127: symbol-only separator/garbage line :: 1 3</t>
+          <t>L125: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3038,7 +3042,7 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L128: isolated marker/symbol line :: 1</t>
+          <t>L126: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3069,7 +3073,7 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L129: isolated marker/symbol line :: 3</t>
+          <t>L127: symbol-only separator/garbage line :: 1 3</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3100,7 +3104,7 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 1</t>
+          <t>L128: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -3131,7 +3135,7 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: 3</t>
+          <t>L129: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -3162,7 +3166,7 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: 1</t>
+          <t>L130: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -3193,7 +3197,7 @@
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L134: isolated marker/symbol line :: 3</t>
+          <t>L131: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -3224,7 +3228,7 @@
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L135: isolated marker/symbol line :: 2</t>
+          <t>L133: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -3255,7 +3259,7 @@
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L136: isolated marker/symbol line :: 6</t>
+          <t>L134: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -3286,7 +3290,7 @@
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: 2</t>
+          <t>L135: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -3317,7 +3321,7 @@
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: 0</t>
+          <t>L136: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
@@ -3348,7 +3352,7 @@
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 2</t>
+          <t>L137: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
@@ -3379,7 +3383,7 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 6</t>
+          <t>L138: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
@@ -3410,7 +3414,7 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: 1</t>
+          <t>L139: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
@@ -3441,7 +3445,7 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L143: isolated marker/symbol line :: 0</t>
+          <t>L140: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
@@ -3472,7 +3476,7 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: 1</t>
+          <t>L142: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
@@ -3503,7 +3507,7 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L145: isolated marker/symbol line :: 0</t>
+          <t>L143: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -3534,7 +3538,7 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 0</t>
+          <t>L144: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -3565,7 +3569,7 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L147: isolated marker/symbol line :: 6</t>
+          <t>L145: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -3596,7 +3600,7 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L148: isolated marker/symbol line :: 5</t>
+          <t>L146: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -3627,7 +3631,7 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L149: isolated marker/symbol line :: 0</t>
+          <t>L147: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -3642,6 +3646,68 @@
       <c r="X88" s="1" t="inlineStr"/>
       <c r="Y88" s="1" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr"/>
+      <c r="B89" s="1" t="inlineStr"/>
+      <c r="C89" s="1" t="inlineStr"/>
+      <c r="D89" s="1" t="inlineStr"/>
+      <c r="E89" s="1" t="inlineStr"/>
+      <c r="F89" s="1" t="inlineStr"/>
+      <c r="G89" s="1" t="inlineStr"/>
+      <c r="H89" s="1" t="inlineStr"/>
+      <c r="I89" s="1" t="inlineStr"/>
+      <c r="J89" s="1" t="inlineStr"/>
+      <c r="K89" s="1" t="inlineStr"/>
+      <c r="L89" s="1" t="inlineStr"/>
+      <c r="M89" s="1" t="inlineStr"/>
+      <c r="N89" s="1" t="inlineStr">
+        <is>
+          <t>L148: isolated marker/symbol line :: 5</t>
+        </is>
+      </c>
+      <c r="O89" s="1" t="inlineStr"/>
+      <c r="P89" s="1" t="inlineStr"/>
+      <c r="Q89" s="1" t="inlineStr"/>
+      <c r="R89" s="1" t="inlineStr"/>
+      <c r="S89" s="1" t="inlineStr"/>
+      <c r="T89" s="1" t="inlineStr"/>
+      <c r="U89" s="1" t="inlineStr"/>
+      <c r="V89" s="1" t="inlineStr"/>
+      <c r="W89" s="1" t="inlineStr"/>
+      <c r="X89" s="1" t="inlineStr"/>
+      <c r="Y89" s="1" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr"/>
+      <c r="B90" s="1" t="inlineStr"/>
+      <c r="C90" s="1" t="inlineStr"/>
+      <c r="D90" s="1" t="inlineStr"/>
+      <c r="E90" s="1" t="inlineStr"/>
+      <c r="F90" s="1" t="inlineStr"/>
+      <c r="G90" s="1" t="inlineStr"/>
+      <c r="H90" s="1" t="inlineStr"/>
+      <c r="I90" s="1" t="inlineStr"/>
+      <c r="J90" s="1" t="inlineStr"/>
+      <c r="K90" s="1" t="inlineStr"/>
+      <c r="L90" s="1" t="inlineStr"/>
+      <c r="M90" s="1" t="inlineStr"/>
+      <c r="N90" s="1" t="inlineStr">
+        <is>
+          <t>L149: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O90" s="1" t="inlineStr"/>
+      <c r="P90" s="1" t="inlineStr"/>
+      <c r="Q90" s="1" t="inlineStr"/>
+      <c r="R90" s="1" t="inlineStr"/>
+      <c r="S90" s="1" t="inlineStr"/>
+      <c r="T90" s="1" t="inlineStr"/>
+      <c r="U90" s="1" t="inlineStr"/>
+      <c r="V90" s="1" t="inlineStr"/>
+      <c r="W90" s="1" t="inlineStr"/>
+      <c r="X90" s="1" t="inlineStr"/>
+      <c r="Y90" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
